--- a/Kemasan.xlsx
+++ b/Kemasan.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
-  <si>
-    <t>jenis</t>
-  </si>
-  <si>
-    <t>kode_kemasan</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="24">
   <si>
     <t>nama</t>
+  </si>
+  <si>
+    <t>kode</t>
+  </si>
+  <si>
+    <t>qty</t>
   </si>
   <si>
     <t>satuan</t>
@@ -89,7 +89,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="12.0"/>
       <color theme="1"/>
@@ -101,13 +101,24 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -116,13 +127,16 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -346,9 +360,12 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -362,7 +379,7 @@
       <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="3">
         <v>1.0</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -379,7 +396,7 @@
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="3">
         <v>1.0</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -396,7 +413,7 @@
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="3">
         <v>1.0</v>
       </c>
       <c r="E4" s="2" t="s">
@@ -413,7 +430,7 @@
       <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="3">
         <v>1.0</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -430,7 +447,7 @@
       <c r="C6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="3">
         <v>1.0</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -447,7 +464,7 @@
       <c r="C7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="3">
         <v>1.0</v>
       </c>
       <c r="E7" s="2" t="s">
@@ -464,7 +481,7 @@
       <c r="C8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="3">
         <v>1.0</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -481,7 +498,7 @@
       <c r="C9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="3">
         <v>1.0</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -498,7 +515,7 @@
       <c r="C10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="3">
         <v>1.0</v>
       </c>
       <c r="E10" s="2" t="s">
